--- a/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_digeged_mto.xlsx
+++ b/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_digeged_mto.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z42"/>
+  <dimension ref="A1:AB42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,6 +547,16 @@
           <t>ubigeo</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>dre</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ugel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -655,6 +665,16 @@
           <t>021910</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>UGEL SIHUAS</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -763,6 +783,16 @@
           <t>021907</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>UGEL SIHUAS</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -871,6 +901,16 @@
           <t>021909</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>UGEL SIHUAS</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -979,6 +1019,16 @@
           <t>021906</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>UGEL SIHUAS</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1087,6 +1137,16 @@
           <t>021906</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>UGEL SIHUAS</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1195,6 +1255,16 @@
           <t>021902</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>UGEL SIHUAS</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1303,6 +1373,16 @@
           <t>021901</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>UGEL SIHUAS</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1411,6 +1491,16 @@
           <t>021909</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>UGEL SIHUAS</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1517,6 +1607,16 @@
       <c r="Z10" t="inlineStr">
         <is>
           <t>040501</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
     </row>
@@ -1617,6 +1717,16 @@
           <t>040514</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1715,6 +1825,16 @@
           <t>040516</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1813,6 +1933,16 @@
           <t>040516</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1911,6 +2041,16 @@
           <t>040504</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2009,6 +2149,16 @@
           <t>040517</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2107,6 +2257,16 @@
           <t>040404</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2205,6 +2365,16 @@
           <t>040503</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2303,6 +2473,16 @@
           <t>040504</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2401,6 +2581,16 @@
           <t>040603</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2499,6 +2689,16 @@
           <t>040517</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2597,6 +2797,16 @@
           <t>040515</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2695,6 +2905,16 @@
           <t>040501</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2793,6 +3013,16 @@
           <t>040501</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2891,6 +3121,16 @@
           <t>040505</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2987,6 +3227,16 @@
       <c r="Z25" t="inlineStr">
         <is>
           <t>040506</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
     </row>
@@ -3053,6 +3303,8 @@
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3151,6 +3403,16 @@
           <t>040406</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3249,6 +3511,16 @@
           <t>040519</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3347,6 +3619,16 @@
           <t>040514</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3459,6 +3741,16 @@
           <t>050901</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>UGEL SUCRE</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3573,6 +3865,16 @@
       <c r="Z31" t="inlineStr">
         <is>
           <t>050505</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>UGEL LA MAR</t>
         </is>
       </c>
     </row>
@@ -3667,6 +3969,8 @@
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3775,6 +4079,16 @@
           <t>060417</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>UGEL CHOTA</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3887,6 +4201,16 @@
           <t>060612</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>UGEL CUTERVO</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3999,6 +4323,16 @@
           <t>060608</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>UGEL CUTERVO</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4111,6 +4445,16 @@
           <t>060906</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>UGEL SAN IGNACIO</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4219,6 +4563,16 @@
           <t>180301</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>DRE MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>UGEL ILO</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4327,6 +4681,16 @@
           <t>180302</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>DRE MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>UGEL ILO</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4435,6 +4799,16 @@
           <t>180301</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>DRE MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>UGEL ILO</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4543,6 +4917,16 @@
           <t>150407</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>UGEL 12 CANTA</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4651,6 +5035,16 @@
           <t>150407</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>UGEL 12 CANTA</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4757,6 +5151,16 @@
       <c r="Z42" t="inlineStr">
         <is>
           <t>150401</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>UGEL 12 CANTA</t>
         </is>
       </c>
     </row>

--- a/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_digeged_mto.xlsx
+++ b/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_digeged_mto.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB42"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,6 +557,11 @@
           <t>ugel</t>
         </is>
       </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -675,6 +680,11 @@
           <t>UGEL SIHUAS</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -793,6 +803,11 @@
           <t>UGEL SIHUAS</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -911,6 +926,11 @@
           <t>UGEL SIHUAS</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1029,6 +1049,11 @@
           <t>UGEL SIHUAS</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1147,6 +1172,11 @@
           <t>UGEL SIHUAS</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1265,6 +1295,11 @@
           <t>UGEL SIHUAS</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1383,6 +1418,11 @@
           <t>UGEL SIHUAS</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1501,6 +1541,11 @@
           <t>UGEL SIHUAS</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1617,6 +1662,11 @@
       <c r="AB10" t="inlineStr">
         <is>
           <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
         </is>
       </c>
     </row>
@@ -1727,6 +1777,11 @@
           <t>UGEL CAYLLOMA</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1835,6 +1890,11 @@
           <t>UGEL CAYLLOMA</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1943,6 +2003,11 @@
           <t>UGEL CAYLLOMA</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2051,6 +2116,11 @@
           <t>UGEL CAYLLOMA</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2159,6 +2229,11 @@
           <t>UGEL CAYLLOMA</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2267,6 +2342,11 @@
           <t>UGEL CAYLLOMA</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2375,6 +2455,11 @@
           <t>UGEL CAYLLOMA</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2483,6 +2568,11 @@
           <t>UGEL CAYLLOMA</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2591,6 +2681,11 @@
           <t>UGEL CAYLLOMA</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2699,6 +2794,11 @@
           <t>UGEL CAYLLOMA</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2807,6 +2907,11 @@
           <t>UGEL CAYLLOMA</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2915,6 +3020,11 @@
           <t>UGEL CAYLLOMA</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3023,6 +3133,11 @@
           <t>UGEL CAYLLOMA</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3131,6 +3246,11 @@
           <t>UGEL CAYLLOMA</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3237,6 +3357,11 @@
       <c r="AB25" t="inlineStr">
         <is>
           <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
         </is>
       </c>
     </row>
@@ -3305,6 +3430,11 @@
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3413,6 +3543,11 @@
           <t>UGEL CAYLLOMA</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3521,6 +3656,11 @@
           <t>UGEL CAYLLOMA</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3629,6 +3769,11 @@
           <t>UGEL CAYLLOMA</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3751,6 +3896,11 @@
           <t>UGEL SUCRE</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3875,6 +4025,11 @@
       <c r="AB31" t="inlineStr">
         <is>
           <t>UGEL LA MAR</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
         </is>
       </c>
     </row>
@@ -3964,13 +4119,42 @@
           <t>106785</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>HUAMANGA</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
       <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
-      <c r="AB32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>050101</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4089,6 +4273,11 @@
           <t>UGEL CHOTA</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4211,6 +4400,11 @@
           <t>UGEL CUTERVO</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4333,6 +4527,11 @@
           <t>UGEL CUTERVO</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4455,6 +4654,11 @@
           <t>UGEL SAN IGNACIO</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4573,6 +4777,11 @@
           <t>UGEL ILO</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4691,6 +4900,11 @@
           <t>UGEL ILO</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4809,6 +5023,11 @@
           <t>UGEL ILO</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4927,6 +5146,11 @@
           <t>UGEL 12 CANTA</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5045,6 +5269,11 @@
           <t>UGEL 12 CANTA</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5161,6 +5390,11 @@
       <c r="AB42" t="inlineStr">
         <is>
           <t>UGEL 12 CANTA</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
         </is>
       </c>
     </row>

--- a/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_digeged_mto.xlsx
+++ b/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_digeged_mto.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AE42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,6 +559,16 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>nombre_ie</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>fuente</t>
         </is>
       </c>
@@ -682,6 +692,16 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
+          <t>84190</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -805,6 +825,16 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -928,6 +958,16 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -1051,6 +1091,16 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -1174,6 +1224,16 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -1297,6 +1357,16 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -1420,6 +1490,16 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
+          <t>225 MARIA PAREJA MALARIN</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -1543,6 +1623,16 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
+          <t>84102</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -1665,6 +1755,16 @@
         </is>
       </c>
       <c r="AC10" t="inlineStr">
+        <is>
+          <t>075 DIVINO NIÑO JESUS</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -1779,6 +1879,16 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
+          <t>40398/40398</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -1892,6 +2002,16 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
+          <t>40419/40419</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -2005,6 +2125,16 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
+          <t>40437/40437</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -2118,6 +2248,16 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
+          <t>40574/40574</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -2231,6 +2371,16 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
+          <t>40586/40586</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -2344,6 +2494,16 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
+          <t>ARCO IRIS DE COLOR</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -2457,6 +2617,16 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
+          <t>CABANACONDE</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -2570,6 +2740,16 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
+          <t>CALLALLI</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -2683,6 +2863,16 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
+          <t>CAYARANI</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -2796,6 +2986,16 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
+          <t>COTA COTA</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -2909,6 +3109,16 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
+          <t>GOTITAS DE ROCIO</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -3022,6 +3232,16 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
+          <t>JARDINES DEL COLCA</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -3135,6 +3355,16 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
+          <t>LOS PATITOS II</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -3248,6 +3478,16 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
+          <t>MI SEGUNDO HOGAR</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -3360,6 +3600,16 @@
         </is>
       </c>
       <c r="AC25" t="inlineStr">
+        <is>
+          <t>MIS CAPULLITOS II / CHANINCHAQ MAQUICHA</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -3430,7 +3680,9 @@
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr"/>
-      <c r="AC26" t="inlineStr">
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -3545,6 +3797,16 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
+          <t>PATITO DONALD</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -3658,6 +3920,16 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
+          <t>SAINT ERBLON PERU - FRANCIA</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -3771,6 +4043,16 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
+          <t>SUMAQTA PUSAKUWAY</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -3898,6 +4180,16 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
+          <t>230-19 VIRGEN INMACULADA CONCEPCION</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -4028,6 +4320,16 @@
         </is>
       </c>
       <c r="AC31" t="inlineStr">
+        <is>
+          <t>38994-19</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -4151,6 +4453,16 @@
         </is>
       </c>
       <c r="AC32" t="inlineStr">
+        <is>
+          <t>MOLLEPATA</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -4275,6 +4587,16 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
+          <t>10465/10465</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -4402,6 +4724,16 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -4529,6 +4861,16 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -4656,6 +4998,16 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
+          <t>17740</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -4779,6 +5131,16 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
+          <t>VISTA AZUL</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -4902,6 +5264,16 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
+          <t>360 SEMILLITAS DE OLIVO</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -5025,6 +5397,16 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -5148,6 +5530,16 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -5271,6 +5663,16 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
+          <t>506-5 NIÑO JESUS</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -5393,6 +5795,16 @@
         </is>
       </c>
       <c r="AC42" t="inlineStr">
+        <is>
+          <t>GABRIEL MORENO</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>

--- a/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_digeged_mto.xlsx
+++ b/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_digeged_mto.xlsx
@@ -419,102 +419,102 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Codigo Modular</t>
+          <t>cod_mod</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>AÑO</t>
+          <t>ano</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>DRE/GRE</t>
+          <t>dre_gre</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Unidad Ejecutora</t>
+          <t>unidad_ejecutora</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>UGEL</t>
+          <t>ugel</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Producto</t>
+          <t>producto</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Actividad</t>
+          <t>actividad</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Unidad de medida</t>
+          <t>unidad_de_medida</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Meta Fisica Programada (Cantidad)</t>
+          <t>meta_fisica_programada_cantidad</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Detalle de la Unidad de Medida (Nombre del Servicio contratado)</t>
+          <t>detalle_de_la_unidad_de_medida_nombre_del_servicio_contratad</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Centro Poblado</t>
+          <t>centro_poblado</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Nivel</t>
+          <t>nivel</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>SIAGIE 2025</t>
+          <t>siagie_2025</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Intervención Culminada (Si/No)</t>
+          <t>intervencion_culminada_si_no</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>PIM 2025</t>
+          <t>pim_2025</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Fuentes de Financiamiento</t>
+          <t>fuentes_de_financiamiento</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>¿Como se ejecutaran los recursos asignados?</t>
+          <t>como_se_ejecutaran_los_recursos_asignados</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>OBS</t>
+          <t>obs</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>ETAPA</t>
+          <t>etapa</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>FECHA DE INFORMACION</t>
+          <t>fecha_de_informacion</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>centro_poblado</t>
+          <t>centro_poblado_2</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>ugel</t>
+          <t>ugel_2</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">

--- a/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_digeged_mto.xlsx
+++ b/output/bases_limpias/Grupo_06_MANTENIMIENTO/df_digeged_mto.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE42"/>
+  <dimension ref="A1:AD42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,60 +514,55 @@
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>fecha_de_informacion</t>
+          <t>cod_local</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>cod_local</t>
+          <t>departamento</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>departamento</t>
+          <t>provincia</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>provincia</t>
+          <t>distrito</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>distrito</t>
+          <t>centro_poblado_2</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>centro_poblado_2</t>
+          <t>ubigeo</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>ubigeo</t>
+          <t>dre</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>dre</t>
+          <t>ugel_2</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>ugel_2</t>
+          <t>nombre_ie</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>nombre_ie</t>
+          <t>area</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
-        <is>
-          <t>area</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
         <is>
           <t>fuente</t>
         </is>
@@ -649,20 +644,24 @@
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>040242</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>040242</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>SIHUAS</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>SIHUAS</t>
+          <t>SICSIBAMBA</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -672,35 +671,30 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>SICSIBAMBA</t>
+          <t>021910</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>021910</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>UGEL SIHUAS</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>UGEL SIHUAS</t>
+          <t>84190</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>84190</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -782,58 +776,57 @@
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>039615</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>039615</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>SIHUAS</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>SIHUAS</t>
+          <t>QUICHES</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>QUICHES</t>
+          <t>CASABLANCA</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>CASABLANCA</t>
+          <t>021907</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>021907</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>UGEL SIHUAS</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>UGEL SIHUAS</t>
+          <t>280</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -915,58 +908,57 @@
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>770810</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>770810</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>SIHUAS</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>SIHUAS</t>
+          <t>SAN JUAN</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>SAN JUAN</t>
+          <t>PASACANCHA CHICO</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>PASACANCHA CHICO</t>
+          <t>021909</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>021909</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>UGEL SIHUAS</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>UGEL SIHUAS</t>
+          <t>701</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -1048,58 +1040,57 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>039371</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>039371</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>SIHUAS</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>SIHUAS</t>
+          <t>HUAYLLABAMBA</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>HUAYLLABAMBA</t>
+          <t>SACSAY</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>SACSAY</t>
+          <t>021906</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>021906</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>UGEL SIHUAS</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>UGEL SIHUAS</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -1181,58 +1172,57 @@
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>039366</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>039366</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>SIHUAS</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>SIHUAS</t>
+          <t>HUAYLLABAMBA</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>HUAYLLABAMBA</t>
+          <t>TUPAC AMARU</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>TUPAC AMARU</t>
+          <t>021906</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>021906</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>UGEL SIHUAS</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>UGEL SIHUAS</t>
+          <t>268</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -1314,58 +1304,57 @@
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>536718</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>536718</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>SIHUAS</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>SIHUAS</t>
+          <t>ACOBAMBA</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>ACOBAMBA</t>
+          <t>QUILCA</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>QUILCA</t>
+          <t>021902</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>021902</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>UGEL SIHUAS</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>UGEL SIHUAS</t>
+          <t>249</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -1447,15 +1436,19 @@
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>038630</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>038630</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>SIHUAS</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1465,40 +1458,35 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>SIHUAS</t>
+          <t>SIHUAS HISTORICO</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>SIHUAS HISTORICO</t>
+          <t>021901</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>021901</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>UGEL SIHUAS</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>UGEL SIHUAS</t>
+          <t>225 MARIA PAREJA MALARIN</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>225 MARIA PAREJA MALARIN</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -1580,58 +1568,57 @@
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>039998</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>039998</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>SIHUAS</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>SIHUAS</t>
+          <t>SAN JUAN</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>SAN JUAN</t>
+          <t>CHUNCANA</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>CHUNCANA</t>
+          <t>021909</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>021909</t>
+          <t>DRE ANCASH</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>DRE ANCASH</t>
+          <t>UGEL SIHUAS</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>UGEL SIHUAS</t>
+          <t>84102</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>84102</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -1713,20 +1700,24 @@
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>069674</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>069674</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CAYLLOMA</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>CAYLLOMA</t>
+          <t>CHIVAY</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -1736,35 +1727,30 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>CHIVAY</t>
+          <t>040501</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>040501</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>GRE AREQUIPA</t>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>UGEL CAYLLOMA</t>
+          <t>075 DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>075 DIVINO NIÑO JESUS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -1836,58 +1822,57 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>070979</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>070979</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CAYLLOMA</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>CAYLLOMA</t>
+          <t>SAN ANTONIO DE CHUCA</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>SAN ANTONIO DE CHUCA</t>
+          <t>COLCA HUALLATA</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>COLCA HUALLATA</t>
+          <t>040514</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>040514</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>GRE AREQUIPA</t>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>UGEL CAYLLOMA</t>
+          <t>40398/40398</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>40398/40398</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -1959,58 +1944,57 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>071139</t>
+        </is>
+      </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>071139</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CAYLLOMA</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>CAYLLOMA</t>
+          <t>TAPAY</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>TAPAY</t>
+          <t>SAN JUAN DE CHUCCHO</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>SAN JUAN DE CHUCCHO</t>
+          <t>040516</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>040516</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>GRE AREQUIPA</t>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>UGEL CAYLLOMA</t>
+          <t>40419/40419</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>40419/40419</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -2082,58 +2066,57 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>533404</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>533404</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CAYLLOMA</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>CAYLLOMA</t>
+          <t>TAPAY</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>TAPAY</t>
+          <t>FURE</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>FURE</t>
+          <t>040516</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>040516</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>GRE AREQUIPA</t>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>UGEL CAYLLOMA</t>
+          <t>40437/40437</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>40437/40437</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -2205,58 +2188,57 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>069947</t>
+        </is>
+      </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>069947</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CAYLLOMA</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>CAYLLOMA</t>
+          <t>CALLALLI</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>CALLALLI</t>
+          <t>CHICHAS</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>CHICHAS</t>
+          <t>040504</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>040504</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>GRE AREQUIPA</t>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>UGEL CAYLLOMA</t>
+          <t>40574/40574</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>40574/40574</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -2328,58 +2310,57 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>071078</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>071078</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CAYLLOMA</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>CAYLLOMA</t>
+          <t>TISCO</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>TISCO</t>
+          <t>CHALLUTA</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>CHALLUTA</t>
+          <t>040517</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>040517</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>GRE AREQUIPA</t>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>UGEL CAYLLOMA</t>
+          <t>40586/40586</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>40586/40586</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -2451,58 +2432,57 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>793449</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>793449</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CASTILLA</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>CASTILLA</t>
+          <t>CHACHAS</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>CHACHAS</t>
+          <t>CHECOTAÑA</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>CHECOTAÑA</t>
+          <t>040404</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>040404</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>GRE AREQUIPA</t>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>UGEL CAYLLOMA</t>
+          <t>ARCO IRIS DE COLOR</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ARCO IRIS DE COLOR</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -2574,20 +2554,24 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>069867</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>069867</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CAYLLOMA</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>CAYLLOMA</t>
+          <t>CABANACONDE</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -2597,35 +2581,30 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
+          <t>040503</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>CABANACONDE</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>040503</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>GRE AREQUIPA</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>UGEL CAYLLOMA</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>CABANACONDE</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -2697,20 +2676,24 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>069971</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>069971</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CAYLLOMA</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>CAYLLOMA</t>
+          <t>CALLALLI</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -2720,35 +2703,30 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
+          <t>040504</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>CALLALLI</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>040504</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>GRE AREQUIPA</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>UGEL CAYLLOMA</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>CALLALLI</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -2820,20 +2798,24 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>071808</t>
+        </is>
+      </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>071808</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CONDESUYOS</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>CONDESUYOS</t>
+          <t>CAYARANI</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -2843,35 +2825,30 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
+          <t>040603</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>CAYARANI</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>040603</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>GRE AREQUIPA</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>UGEL CAYLLOMA</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>CAYARANI</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -2943,58 +2920,57 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>071257</t>
+        </is>
+      </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>071257</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CAYLLOMA</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>CAYLLOMA</t>
+          <t>TISCO</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>TISCO</t>
+          <t>COTA COTA</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
+          <t>040517</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>GRE AREQUIPA</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>UGEL CAYLLOMA</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
           <t>COTA COTA</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>040517</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>GRE AREQUIPA</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>UGEL CAYLLOMA</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>COTA COTA</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -3066,58 +3042,57 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>816969</t>
+        </is>
+      </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>816969</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CAYLLOMA</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>CAYLLOMA</t>
+          <t>SIBAYO</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>SIBAYO</t>
+          <t>CONDORCUYO</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>CONDORCUYO</t>
+          <t>040515</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>040515</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>GRE AREQUIPA</t>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>UGEL CAYLLOMA</t>
+          <t>GOTITAS DE ROCIO</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>GOTITAS DE ROCIO</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -3189,20 +3164,24 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>731932</t>
+        </is>
+      </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>731932</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CAYLLOMA</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>CAYLLOMA</t>
+          <t>CHIVAY</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -3212,35 +3191,30 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>CHIVAY</t>
+          <t>040501</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>040501</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>GRE AREQUIPA</t>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>UGEL CAYLLOMA</t>
+          <t>JARDINES DEL COLCA</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>JARDINES DEL COLCA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -3312,58 +3286,57 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>816945</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>816945</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CAYLLOMA</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>CAYLLOMA</t>
+          <t>CHIVAY</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>CHIVAY</t>
+          <t>SAN ANDRES</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>SAN ANDRES</t>
+          <t>040501</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>040501</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>GRE AREQUIPA</t>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>UGEL CAYLLOMA</t>
+          <t>LOS PATITOS II</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>LOS PATITOS II</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -3435,15 +3408,19 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>758974</t>
+        </is>
+      </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>758974</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CAYLLOMA</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3453,40 +3430,35 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>CAYLLOMA</t>
+          <t>CIUDAD MINERA</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>CIUDAD MINERA</t>
+          <t>040505</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>040505</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>GRE AREQUIPA</t>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>UGEL CAYLLOMA</t>
+          <t>MI SEGUNDO HOGAR</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>MI SEGUNDO HOGAR</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -3558,58 +3530,57 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>816931</t>
+        </is>
+      </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>816931</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CAYLLOMA</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>CAYLLOMA</t>
+          <t>COPORAQUE</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>COPORAQUE</t>
+          <t>SACSAYHUAMAN</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>SACSAYHUAMAN</t>
+          <t>040506</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>040506</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>GRE AREQUIPA</t>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>UGEL CAYLLOMA</t>
+          <t>MIS CAPULLITOS II / CHANINCHAQ MAQUICHA</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>MIS CAPULLITOS II / CHANINCHAQ MAQUICHA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -3681,8 +3652,7 @@
       <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr"/>
-      <c r="AD26" t="inlineStr"/>
-      <c r="AE26" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -3754,58 +3724,57 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>808870</t>
+        </is>
+      </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>808870</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CASTILLA</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>CASTILLA</t>
+          <t>CHOCO</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>CHOCO</t>
+          <t>PACHAUMA</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>PACHAUMA</t>
+          <t>040406</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>040406</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>GRE AREQUIPA</t>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>UGEL CAYLLOMA</t>
+          <t>PATITO DONALD</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>PATITO DONALD</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -3877,20 +3846,24 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>071417</t>
+        </is>
+      </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>071417</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CAYLLOMA</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>CAYLLOMA</t>
+          <t>YANQUE</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -3900,35 +3873,30 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>YANQUE</t>
+          <t>040519</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>040519</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>GRE AREQUIPA</t>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>UGEL CAYLLOMA</t>
+          <t>SAINT ERBLON PERU - FRANCIA</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>SAINT ERBLON PERU - FRANCIA</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -4000,58 +3968,57 @@
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>816950</t>
+        </is>
+      </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>816950</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>CAYLLOMA</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>CAYLLOMA</t>
+          <t>SAN ANTONIO DE CHUCA</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>SAN ANTONIO DE CHUCA</t>
+          <t>IMATA</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>IMATA</t>
+          <t>040514</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>040514</t>
+          <t>GRE AREQUIPA</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>GRE AREQUIPA</t>
+          <t>UGEL CAYLLOMA</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>UGEL CAYLLOMA</t>
+          <t>SUMAQTA PUSAKUWAY</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>SUMAQTA PUSAKUWAY</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -4137,20 +4104,24 @@
       </c>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>904796</t>
+        </is>
+      </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>904796</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>SUCRE</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>SUCRE</t>
+          <t>QUEROBAMBA</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -4160,35 +4131,30 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>QUEROBAMBA</t>
+          <t>050901</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>050901</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>DRE AYACUCHO</t>
+          <t>UGEL SUCRE</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>UGEL SUCRE</t>
+          <t>230-19 VIRGEN INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>230-19 VIRGEN INMACULADA CONCEPCION</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -4278,58 +4244,57 @@
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>848277</t>
+        </is>
+      </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>848277</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>LA MAR</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>LA MAR</t>
+          <t>CHUNGUI</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>CHUNGUI</t>
+          <t>LAS MALVINAS</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>LAS MALVINAS</t>
+          <t>050505</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>050505</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>DRE AYACUCHO</t>
+          <t>UGEL LA MAR</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>UGEL LA MAR</t>
+          <t>38994-19</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>38994-19</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -4415,54 +4380,53 @@
       </c>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>106785</t>
+        </is>
+      </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>106785</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
+          <t>HUAMANGA</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
           <t>AYACUCHO</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>HUAMANGA</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>050101</t>
+        </is>
+      </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>050101</t>
+          <t>DRE AYACUCHO</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>DRE AYACUCHO</t>
+          <t>UGEL HUAMANGA</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>UGEL HUAMANGA</t>
+          <t>MOLLEPATA</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>MOLLEPATA</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE32" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -4544,58 +4508,57 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>109378</t>
+        </is>
+      </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>109378</t>
+          <t>CAJAMARCA</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>CAJAMARCA</t>
+          <t>CHOTA</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>CHOTA</t>
+          <t>TACABAMBA</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>TACABAMBA</t>
+          <t>PUÑA</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>PUÑA</t>
+          <t>060417</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>060417</t>
+          <t>DRE CAJAMARCA</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>DRE CAJAMARCA</t>
+          <t>UGEL CHOTA</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>UGEL CHOTA</t>
+          <t>10465/10465</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>10465/10465</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -4681,58 +4644,57 @@
       </c>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>772772</t>
+        </is>
+      </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>772772</t>
+          <t>CAJAMARCA</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>CAJAMARCA</t>
+          <t>CUTERVO</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>CUTERVO</t>
+          <t>SANTO DOMINGO DE LA CAPILLA</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO DE LA CAPILLA</t>
+          <t>TABLA BAMBA</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>TABLA BAMBA</t>
+          <t>060612</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>060612</t>
+          <t>DRE CAJAMARCA</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>DRE CAJAMARCA</t>
+          <t>UGEL CUTERVO</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>UGEL CUTERVO</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -4818,58 +4780,57 @@
       </c>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>580235</t>
+        </is>
+      </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>580235</t>
+          <t>CAJAMARCA</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>CAJAMARCA</t>
+          <t>CUTERVO</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>CUTERVO</t>
+          <t>SAN ANDRES DE CUTERVO</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>SAN ANDRES DE CUTERVO</t>
+          <t>QUILLUGAY</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>QUILLUGAY</t>
+          <t>060608</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>060608</t>
+          <t>DRE CAJAMARCA</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>DRE CAJAMARCA</t>
+          <t>UGEL CUTERVO</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>UGEL CUTERVO</t>
+          <t>375</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE35" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -4955,58 +4916,57 @@
       </c>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>130407</t>
+        </is>
+      </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>130407</t>
+          <t>CAJAMARCA</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>CAJAMARCA</t>
+          <t>SAN IGNACIO</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>SAN IGNACIO</t>
+          <t>SAN JOSE DE LOURDES</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>SAN JOSE DE LOURDES</t>
+          <t>NUEVO PROGRESO</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>NUEVO PROGRESO</t>
+          <t>060906</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>060906</t>
+          <t>DRE CAJAMARCA</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>DRE CAJAMARCA</t>
+          <t>UGEL SAN IGNACIO</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>UGEL SAN IGNACIO</t>
+          <t>17740</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>17740</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE36" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -5088,15 +5048,19 @@
       </c>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>730107</t>
+        </is>
+      </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>730107</t>
+          <t>MOQUEGUA</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>MOQUEGUA</t>
+          <t>ILO</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -5106,40 +5070,35 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>ILO</t>
+          <t>PAMPA INALAMBRICA</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>PAMPA INALAMBRICA</t>
+          <t>180301</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>180301</t>
+          <t>DRE MOQUEGUA</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>DRE MOQUEGUA</t>
+          <t>UGEL ILO</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>UGEL ILO</t>
+          <t>VISTA AZUL</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>VISTA AZUL</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE37" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -5221,58 +5180,57 @@
       </c>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>730800</t>
+        </is>
+      </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>730800</t>
+          <t>MOQUEGUA</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>MOQUEGUA</t>
+          <t>ILO</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>ILO</t>
+          <t>EL ALGARROBAL</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>EL ALGARROBAL</t>
+          <t>PROMUVI I</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>PROMUVI I</t>
+          <t>180302</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>180302</t>
+          <t>DRE MOQUEGUA</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>DRE MOQUEGUA</t>
+          <t>UGEL ILO</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>UGEL ILO</t>
+          <t>360 SEMILLITAS DE OLIVO</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>360 SEMILLITAS DE OLIVO</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE38" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -5354,15 +5312,19 @@
       </c>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>730796</t>
+        </is>
+      </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>730796</t>
+          <t>MOQUEGUA</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>MOQUEGUA</t>
+          <t>ILO</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -5372,40 +5334,35 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>ILO</t>
+          <t>PAMPA INALAMBRICA</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>PAMPA INALAMBRICA</t>
+          <t>180301</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>180301</t>
+          <t>DRE MOQUEGUA</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>DRE MOQUEGUA</t>
+          <t>UGEL ILO</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>UGEL ILO</t>
+          <t>362</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE39" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -5487,58 +5444,57 @@
       </c>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>708804</t>
+        </is>
+      </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>708804</t>
+          <t>LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>CANTA</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>CANTA</t>
+          <t>SANTA ROSA DE QUIVES</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE QUIVES</t>
+          <t>ZAPAN</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>ZAPAN</t>
+          <t>150407</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>150407</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>UGEL 12 CANTA</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>UGEL 12 CANTA</t>
+          <t>355</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE40" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -5620,20 +5576,24 @@
       </c>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>351535</t>
+        </is>
+      </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>351535</t>
+          <t>LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>CANTA</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>CANTA</t>
+          <t>SANTA ROSA DE QUIVES</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
@@ -5643,35 +5603,30 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE QUIVES</t>
+          <t>150407</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>150407</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>UGEL 12 CANTA</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>UGEL 12 CANTA</t>
+          <t>506-5 NIÑO JESUS</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>506-5 NIÑO JESUS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE41" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -5753,15 +5708,19 @@
       </c>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>736053</t>
+        </is>
+      </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>736053</t>
+          <t>LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>CANTA</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -5776,35 +5735,30 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>CANTA</t>
+          <t>150401</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>150401</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>UGEL 12 CANTA</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>UGEL 12 CANTA</t>
+          <t>GABRIEL MORENO</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>GABRIEL MORENO</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE42" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
